--- a/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
+++ b/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projekt_kalender_pro_beruf\Input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504D93D1-BB43-4212-BA9F-3ADF663CD0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A1C2AC-D7A0-4AAE-9CB0-5824623EAAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechnungsvorlage Honorar" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -167,9 +167,6 @@
     <t>01/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">für die unten aufgeführten Leistungen als Honorardozent:in im Projekt Assistierte Ausbildung AsA VIII berechne ich Ihnen wie folgt: </t>
-  </si>
-  <si>
     <t>04.02.2026 bis 26.02.2026</t>
   </si>
   <si>
@@ -192,6 +189,9 @@
   </si>
   <si>
     <t>SumUp Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">für die unten aufgeführten Leistungen für den Stütz- und Förderunterricht in der Ausbildungsassistenz im Projekt Assistierte Ausbildung AsA VIII berechne ich Ihnen wie folgt: </t>
   </si>
 </sst>
 </file>
@@ -839,7 +839,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.07421875" style="1" customWidth="1"/>
@@ -865,7 +865,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="10"/>
@@ -876,7 +876,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="10"/>
@@ -888,7 +888,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="10"/>
@@ -899,7 +899,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="10"/>
@@ -910,7 +910,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="10"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="29" spans="1:9" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="52" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B29" s="52"/>
       <c r="C29" s="52"/>
@@ -1111,7 +1111,7 @@
       <c r="C33" s="26"/>
       <c r="D33" s="16"/>
       <c r="E33" s="37">
-        <f t="shared" ref="E33:E48" si="0">ROUND(B33*$D$32,2)</f>
+        <f t="shared" ref="E33:E57" si="0">ROUND(B33*$D$32,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -1265,162 +1265,252 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="50" t="s">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="44"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="44"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="44"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="44"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="44"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="44"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="44"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="44"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="44"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="7" customFormat="1" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="38">
-        <f>SUM(E32:E48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="3"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="38">
+        <f>SUM(E32:E57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="3"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+    </row>
+    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="B60" s="2"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="B62" s="20"/>
+      <c r="C62" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="12"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+      <c r="B63" s="20"/>
+      <c r="C63" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="12"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B56" s="3"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D57" s="53" t="s">
+      <c r="B64" s="3"/>
+      <c r="C64" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="12"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B65" s="3"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D66" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="53"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B61" s="3"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="32"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="11"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="34" t="s">
+      <c r="E66" s="53"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D67" s="33"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D68" s="33"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B70" s="3"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="32"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="11"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A64" s="42" t="s">
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="42" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1428,10 +1518,10 @@
   <mergeCells count="7">
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D65:E65"/>
     <mergeCell ref="G24:I24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
+++ b/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projekt_kalender_pro_beruf\Input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A1C2AC-D7A0-4AAE-9CB0-5824623EAAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA9EDCC-6C6F-41A7-85A4-340142E2D40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="497" windowWidth="22149" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsvorlage Honorar" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Sehr geehrte Damen und Herren,</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>sachlich und rechnerisch richtig</t>
-  </si>
-  <si>
-    <t>Unterschrift Honorarkraft</t>
   </si>
   <si>
     <t>Kontoinhaber:in:</t>
@@ -384,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -521,9 +518,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -839,7 +833,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.07421875" style="1" customWidth="1"/>
@@ -865,7 +859,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="10"/>
@@ -876,7 +870,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="10"/>
@@ -888,7 +882,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="10"/>
@@ -899,7 +893,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="10"/>
@@ -910,7 +904,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="10"/>
@@ -1018,10 +1012,10 @@
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="47">
         <v>46079</v>
@@ -1033,13 +1027,13 @@
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
     </row>
     <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="4"/>
@@ -1066,7 +1060,7 @@
     </row>
     <row r="29" spans="1:9" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="52"/>
       <c r="C29" s="52"/>
@@ -1111,7 +1105,7 @@
       <c r="C33" s="26"/>
       <c r="D33" s="16"/>
       <c r="E33" s="37">
-        <f t="shared" ref="E33:E57" si="0">ROUND(B33*$D$32,2)</f>
+        <f t="shared" ref="E33:E61" si="0">ROUND(B33*$D$32,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -1211,7 +1205,7 @@
       <c r="C43" s="15"/>
       <c r="D43" s="16"/>
       <c r="E43" s="37">
-        <f>ROUND(B43*$D$32,2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1355,173 +1349,186 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="50" t="s">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="44"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="44"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="44"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="44"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="7" customFormat="1" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="38">
-        <f>SUM(E32:E57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="3"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-    </row>
-    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
+      <c r="B62" s="51"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="38">
+        <f>SUM(E32:E61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="3"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+    </row>
+    <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-    </row>
-    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+      <c r="B64" s="2"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+      <c r="B66" s="20"/>
+      <c r="C66" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" s="12"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B65" s="3"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D66" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66" s="53"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="12"/>
+      <c r="E67" s="10"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D68" s="33"/>
-      <c r="E68" s="33"/>
+      <c r="A68" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="12"/>
+      <c r="E68" s="10"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B70" s="3"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="12"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="32"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="11"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="34" t="s">
+      <c r="A72" s="32"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="11"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="34"/>
-      <c r="C72" s="34"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="42" t="s">
-        <v>23</v>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="42" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D69:E69"/>
     <mergeCell ref="G24:I24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
+++ b/Input_data/Muster_Honorarrechnung-Lehrkräfte_pytest.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\67t-q6r-h2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA9EDCC-6C6F-41A7-85A4-340142E2D40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6E02B7-848D-44BB-AE78-3E13E2FF9A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="497" windowWidth="22149" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsvorlage Honorar" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -833,28 +833,28 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.07421875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.69140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="53.3046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.69140625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="11" customWidth="1"/>
     <col min="5" max="5" width="14" style="11" customWidth="1"/>
-    <col min="6" max="6" width="11.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.84375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.3828125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.69140625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.3828125" style="1"/>
+    <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="19"/>
       <c r="C1" s="4"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>17</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
         <v>14</v>
       </c>
@@ -877,7 +877,7 @@
       <c r="E3" s="10"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>15</v>
       </c>
@@ -888,7 +888,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="45" t="s">
         <v>18</v>
       </c>
@@ -899,7 +899,7 @@
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="45" t="s">
         <v>19</v>
       </c>
@@ -912,24 +912,24 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C7" s="4"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="G9" s="49"/>
       <c r="H9" s="49"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C10" s="4"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -937,7 +937,7 @@
       <c r="H10" s="49"/>
       <c r="I10" s="49"/>
     </row>
-    <row r="11" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>1</v>
       </c>
@@ -945,7 +945,7 @@
       <c r="D11" s="31"/>
       <c r="E11" s="31"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>3</v>
       </c>
@@ -953,7 +953,7 @@
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
     </row>
-    <row r="13" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
         <v>4</v>
       </c>
@@ -961,52 +961,52 @@
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C16" s="4"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C19" s="4"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C22" s="4"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>13</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
@@ -1035,17 +1035,17 @@
       <c r="H24" s="54"/>
       <c r="I24" s="54"/>
     </row>
-    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="4"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
     </row>
-    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="4"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,12 +1053,12 @@
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
     </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="4"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
     </row>
-    <row r="29" spans="1:9" ht="34.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="34.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="52" t="s">
         <v>33</v>
       </c>
@@ -1067,12 +1067,12 @@
       <c r="D29" s="52"/>
       <c r="E29" s="52"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C30" s="4"/>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
     </row>
-    <row r="31" spans="1:9" ht="42.45" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.2">
       <c r="A31" s="35" t="s">
         <v>9</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="44"/>
       <c r="B32" s="25"/>
       <c r="C32" s="26"/>
@@ -1099,17 +1099,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="44"/>
       <c r="B33" s="25"/>
       <c r="C33" s="26"/>
       <c r="D33" s="16"/>
       <c r="E33" s="37">
-        <f t="shared" ref="E33:E61" si="0">ROUND(B33*$D$32,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+        <f t="shared" ref="E33:E65" si="0">ROUND(B33*$D$32,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="44"/>
       <c r="B34" s="25"/>
       <c r="C34" s="26"/>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="44"/>
       <c r="B35" s="25"/>
       <c r="C35" s="26"/>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="44"/>
       <c r="B36" s="25"/>
       <c r="C36" s="26"/>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="44"/>
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="44"/>
       <c r="B38" s="25"/>
       <c r="C38" s="26"/>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="44"/>
       <c r="B39" s="17"/>
       <c r="C39" s="26"/>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="44"/>
       <c r="B40" s="17"/>
       <c r="C40" s="15"/>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="44"/>
       <c r="B41" s="17"/>
       <c r="C41" s="15"/>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="44"/>
       <c r="B42" s="17"/>
       <c r="C42" s="15"/>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="44"/>
       <c r="B43" s="17"/>
       <c r="C43" s="15"/>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="44"/>
       <c r="B44" s="17"/>
       <c r="C44" s="15"/>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="44"/>
       <c r="B45" s="17"/>
       <c r="C45" s="15"/>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="44"/>
       <c r="B46" s="17"/>
       <c r="C46" s="15"/>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="44"/>
       <c r="B47" s="17"/>
       <c r="C47" s="15"/>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="44"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="44"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="44"/>
       <c r="B50" s="21"/>
       <c r="C50" s="22"/>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="44"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="44"/>
       <c r="B52" s="21"/>
       <c r="C52" s="22"/>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="44"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="44"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="44"/>
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="44"/>
       <c r="B56" s="21"/>
       <c r="C56" s="22"/>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="44"/>
       <c r="B57" s="21"/>
       <c r="C57" s="22"/>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="44"/>
       <c r="B58" s="21"/>
       <c r="C58" s="22"/>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="44"/>
       <c r="B59" s="21"/>
       <c r="C59" s="22"/>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="44"/>
       <c r="B60" s="21"/>
       <c r="C60" s="22"/>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="44"/>
       <c r="B61" s="21"/>
       <c r="C61" s="22"/>
@@ -1389,136 +1389,176 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="50" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="44"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="44"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="44"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="44"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="38">
-        <f>SUM(E32:E61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="3"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-    </row>
-    <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
+      <c r="B66" s="51"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="38">
+        <f>SUM(E32:E65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="3"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+    </row>
+    <row r="68" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+      <c r="B68" s="2"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="39" t="s">
+      <c r="B70" s="20"/>
+      <c r="C70" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="40" t="s">
+      <c r="B71" s="20"/>
+      <c r="C71" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B69" s="3"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="53"/>
-      <c r="E69" s="53"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D70" s="33"/>
-      <c r="E70" s="33"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B71" s="3"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="10"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="32"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="11"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="34" t="s">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="12"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B73" s="3"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D74" s="33"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B75" s="3"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="32"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="11"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="34"/>
-      <c r="C73" s="34"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="42" t="s">
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="42" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1526,9 +1566,9 @@
   <mergeCells count="6">
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A66:C66"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D73:E73"/>
     <mergeCell ref="G24:I24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1536,7 +1576,7 @@
     <hyperlink ref="B5" r:id="rId1" xr:uid="{841B66B4-07EF-4F3C-B1BB-FAF68803DAF5}"/>
   </hyperlinks>
   <pageMargins left="0.98425196850393704" right="0.78740157480314965" top="0.98425196850393704" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="74" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="62" orientation="portrait" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" max="51" man="1"/>
